--- a/REQUIREMENTS_ANALYSIS.xlsx
+++ b/REQUIREMENTS_ANALYSIS.xlsx
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Personal\ImageReviewer\ImageReviewer\ImageReviewer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4486352-3A81-4AE7-B029-6436E9C2B726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{04B245AE-9D85-4FD4-B74C-45F8DC3DFE45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7365" yWindow="3690" windowWidth="14310" windowHeight="10770" xr2:uid="{D608A4A0-FF44-422B-8891-ECD4B60872DA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{723B3D42-E353-4535-A879-25259A2B8AE4}"/>
   </bookViews>
   <sheets>
     <sheet name="REQUIREMENTS_ANALYSIS" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">REQUIREMENTS_ANALYSIS!$A$1:$G$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">REQUIREMENTS_ANALYSIS!$A$1:$G$24</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="238">
   <si>
     <t>Requirement ID</t>
   </si>
@@ -61,9 +61,6 @@
     <t>Must Have</t>
   </si>
   <si>
-    <t>âœ… Implemented</t>
-  </si>
-  <si>
     <t>ImageLoaderService with BitmapImage and format conversion</t>
   </si>
   <si>
@@ -274,9 +271,6 @@
     <t>Nice to Have</t>
   </si>
   <si>
-    <t>âŒ Future</t>
-  </si>
-  <si>
     <t>Planned for future (4-6 hours)</t>
   </si>
   <si>
@@ -346,9 +340,6 @@
     <t>Operations complete in &lt; 200ms for 1024Ã—1024 images</t>
   </si>
   <si>
-    <t>âœ… Met</t>
-  </si>
-  <si>
     <t>Window/Level: 15ms Gaussian: 120ms Median: 250ms</t>
   </si>
   <si>
@@ -529,9 +520,6 @@
     <t>Handle 4000Ã—4000 images within 10 seconds</t>
   </si>
   <si>
-    <t>âš ï¸ Partial</t>
-  </si>
-  <si>
     <t>Current: 7-13s for some operations. Optimization strategies documented</t>
   </si>
   <si>
@@ -556,9 +544,6 @@
     <t>Support multiple languages</t>
   </si>
   <si>
-    <t>âŒ Not Implemented</t>
-  </si>
-  <si>
     <t>English only currently</t>
   </si>
   <si>
@@ -601,9 +586,6 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>Accepted</t>
-  </si>
-  <si>
     <t>WPF is Windows-specific technology</t>
   </si>
   <si>
@@ -652,9 +634,6 @@
     <t>Approximately 1 week</t>
   </si>
   <si>
-    <t>Met</t>
-  </si>
-  <si>
     <t>Completed in 5-6 days</t>
   </si>
   <si>
@@ -667,9 +646,6 @@
     <t>Minimum 80% for core logic</t>
   </si>
   <si>
-    <t>âœ… Exceeded</t>
-  </si>
-  <si>
     <t>Achieved 85% coverage</t>
   </si>
   <si>
@@ -697,9 +673,6 @@
     <t>Users have basic image processing knowledge</t>
   </si>
   <si>
-    <t>Documented</t>
-  </si>
-  <si>
     <t>No extensive tooltips or tutorials provided</t>
   </si>
   <si>
@@ -749,6 +722,21 @@
   </si>
   <si>
     <t>All processing local for privacy and speed</t>
+  </si>
+  <si>
+    <t>IMPLEMENTED</t>
+  </si>
+  <si>
+    <t>FUTURE</t>
+  </si>
+  <si>
+    <t>PARTIAL</t>
+  </si>
+  <si>
+    <t>ACCEPTED</t>
+  </si>
+  <si>
+    <t>DOCUMENTED</t>
   </si>
 </sst>
 </file>
@@ -892,14 +880,14 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1100,6 +1088,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCCCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1279,17 +1273,16 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="36" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1671,20 +1664,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC0D7FC2-A0EF-4D09-A69C-CBDF5F812509}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB927A36-768F-419D-9C0E-B9616E8ACE16}">
   <dimension ref="A1:G59"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
     <col min="2" max="2" width="18.7109375" customWidth="1"/>
     <col min="3" max="3" width="15.7109375" customWidth="1"/>
-    <col min="4" max="4" width="50.7109375" style="8" customWidth="1"/>
+    <col min="4" max="4" width="50.7109375" style="9" customWidth="1"/>
     <col min="5" max="5" width="12.7109375" customWidth="1"/>
-    <col min="6" max="6" width="15.7109375" customWidth="1"/>
-    <col min="7" max="7" width="40.7109375" style="8" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" customWidth="1"/>
+    <col min="7" max="7" width="40.7109375" style="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1694,7 +1687,7 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -1703,7 +1696,7 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1717,1294 +1710,1290 @@
       <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="8" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="G2" s="8" t="s">
         <v>12</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="8" t="s">
         <v>15</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>16</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>17</v>
+        <v>233</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="8" t="s">
         <v>19</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>20</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>21</v>
+        <v>233</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="8" t="s">
         <v>23</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>24</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>25</v>
+        <v>233</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>27</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>28</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>29</v>
+        <v>233</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>31</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>32</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>33</v>
+        <v>233</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>35</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>36</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>37</v>
+        <v>233</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="E9" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="G9" s="8" t="s">
         <v>41</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="E10" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="G10" s="8" t="s">
         <v>45</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="8" t="s">
         <v>48</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>49</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>50</v>
+        <v>233</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" s="8" t="s">
         <v>52</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>53</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>54</v>
+        <v>233</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" s="8" t="s">
         <v>56</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>57</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>58</v>
+        <v>233</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D14" s="8" t="s">
         <v>60</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>61</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>62</v>
+        <v>233</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D15" s="8" t="s">
         <v>64</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>65</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>66</v>
+        <v>233</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D16" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="E16" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="G16" s="8" t="s">
         <v>69</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D17" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="E17" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="G17" s="8" t="s">
         <v>73</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D18" s="8" t="s">
         <v>76</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>77</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>78</v>
+        <v>233</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D19" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="E19" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="G19" s="8" t="s">
         <v>82</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="G20" s="8" t="s">
         <v>86</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="G21" s="8" t="s">
         <v>90</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>95</v>
+        <v>92</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>93</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>88</v>
+        <v>234</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="G23" s="8" t="s">
         <v>97</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>100</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>92</v>
+        <v>234</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
-      <c r="D25" s="7"/>
+      <c r="D25" s="8"/>
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
-      <c r="G25" s="7"/>
+      <c r="G25" s="8"/>
     </row>
     <row r="26" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="D26" s="8" t="s">
         <v>104</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>106</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="G26" s="7" t="s">
-        <v>108</v>
+        <v>233</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>111</v>
+        <v>107</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>108</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>112</v>
+        <v>233</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="G28" s="8" t="s">
         <v>113</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="G28" s="7" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="G29" s="8" t="s">
         <v>117</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>123</v>
+        <v>119</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>120</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="G30" s="7" t="s">
-        <v>124</v>
+        <v>233</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="G31" s="8" t="s">
         <v>125</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>131</v>
+        <v>127</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>128</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="G32" s="7" t="s">
-        <v>132</v>
+        <v>233</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>135</v>
+        <v>131</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>132</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="G33" s="7" t="s">
-        <v>136</v>
+        <v>233</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="G34" s="8" t="s">
         <v>137</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="G34" s="7" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>143</v>
+        <v>139</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>140</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>144</v>
+        <v>233</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="G36" s="8" t="s">
         <v>145</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="G36" s="7" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="G37" s="8" t="s">
         <v>149</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="G37" s="7" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="G38" s="8" t="s">
         <v>153</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="G38" s="7" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>159</v>
+        <v>155</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>156</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="G39" s="7" t="s">
-        <v>160</v>
+        <v>233</v>
+      </c>
+      <c r="G39" s="8" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>163</v>
+        <v>159</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>160</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="G40" s="7" t="s">
-        <v>164</v>
+        <v>233</v>
+      </c>
+      <c r="G40" s="8" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="G41" s="8" t="s">
         <v>165</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F41" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="G41" s="7" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>172</v>
+        <v>167</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>168</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="G42" s="7" t="s">
-        <v>173</v>
+        <v>235</v>
+      </c>
+      <c r="G42" s="8" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>176</v>
+        <v>171</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>172</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="G43" s="7" t="s">
-        <v>178</v>
+        <v>233</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="D44" s="7" t="s">
-        <v>181</v>
+        <v>175</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>176</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="G44" s="7" t="s">
-        <v>182</v>
+        <v>233</v>
+      </c>
+      <c r="G44" s="8" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>185</v>
+        <v>179</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>180</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="G45" s="7" t="s">
-        <v>186</v>
+        <v>233</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
-      <c r="D46" s="7"/>
+      <c r="D46" s="8"/>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
-      <c r="G46" s="7"/>
+      <c r="G46" s="8"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="G47" s="8" t="s">
         <v>187</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="D47" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="G47" s="7" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>196</v>
+        <v>189</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>190</v>
       </c>
       <c r="E48" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="G48" s="8" t="s">
         <v>191</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="G48" s="7" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="D49" s="7" t="s">
-        <v>200</v>
+        <v>193</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>194</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="G49" s="7" t="s">
-        <v>201</v>
+        <v>186</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="G49" s="8" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>204</v>
+        <v>197</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>198</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="G50" s="7" t="s">
-        <v>205</v>
+        <v>186</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="G50" s="8" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="D51" s="7" t="s">
-        <v>208</v>
+        <v>201</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>202</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="G51" s="7" t="s">
-        <v>210</v>
+        <v>233</v>
+      </c>
+      <c r="G51" s="8" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="D52" s="7" t="s">
-        <v>213</v>
+        <v>205</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>206</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="G52" s="7" t="s">
-        <v>215</v>
+        <v>186</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="G52" s="8" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="D53" s="7" t="s">
-        <v>218</v>
+        <v>209</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>210</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="G53" s="7" t="s">
-        <v>219</v>
+        <v>186</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="G53" s="8" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
-      <c r="D54" s="7"/>
+      <c r="D54" s="8"/>
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
-      <c r="G54" s="7"/>
+      <c r="G54" s="8"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="D55" s="7" t="s">
-        <v>223</v>
+        <v>214</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>215</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="G55" s="7" t="s">
-        <v>225</v>
+        <v>186</v>
+      </c>
+      <c r="F55" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="G55" s="8" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="D56" s="7" t="s">
-        <v>228</v>
+        <v>218</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>219</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="G56" s="7" t="s">
-        <v>229</v>
+        <v>186</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="G56" s="8" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="D57" s="7" t="s">
-        <v>232</v>
+        <v>222</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>223</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="F57" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="F57" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="G57" s="8" t="s">
         <v>224</v>
-      </c>
-      <c r="G57" s="7" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="D58" s="7" t="s">
-        <v>236</v>
+        <v>226</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>227</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="G58" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="F58" s="6" t="s">
         <v>237</v>
+      </c>
+      <c r="G58" s="8" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="D59" s="7" t="s">
-        <v>240</v>
+        <v>230</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>231</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="G59" s="7" t="s">
-        <v>241</v>
+        <v>186</v>
+      </c>
+      <c r="F59" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="G59" s="8" t="s">
+        <v>232</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G59" xr:uid="{AC0D7FC2-A0EF-4D09-A69C-CBDF5F812509}"/>
+  <autoFilter ref="A1:G24" xr:uid="{EB927A36-768F-419D-9C0E-B9616E8ACE16}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <headerFooter>
-    <oddHeader>&amp;C&amp;"Aptos"&amp;12&amp;K000000 LGE Internal Use Only&amp;1#_x000D_</oddHeader>
-  </headerFooter>
 </worksheet>
 </file>
--- a/REQUIREMENTS_ANALYSIS.xlsx
+++ b/REQUIREMENTS_ANALYSIS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Personal\ImageReviewer\ImageReviewer\ImageReviewer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{04B245AE-9D85-4FD4-B74C-45F8DC3DFE45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B449675-6756-42D9-94CB-80A35B810FFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{723B3D42-E353-4535-A879-25259A2B8AE4}"/>
   </bookViews>
@@ -2995,5 +2995,8 @@
   </sheetData>
   <autoFilter ref="A1:G24" xr:uid="{EB927A36-768F-419D-9C0E-B9616E8ACE16}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;12&amp;K000000 LGE Internal Use Only&amp;1#_x000D_</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>